--- a/03-analise-competitiva.xlsx
+++ b/03-analise-competitiva.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,14 +27,24 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002F5D3A"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -54,9 +64,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -427,146 +440,165 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
     <col width="48" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Concorrente</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Site da empresa</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Localização</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Principais Produtos e Serviços</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Em que somos melhores que o concorrente?</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Em que somos piores que a concorrência</t>
+          <t>VISÃO GERAL DA CONCORRÊNCIA</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Pedra Azul</t>
+          <t>Concorrente</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>A confirmar</t>
+          <t>Site da empresa</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Domingos Martins, ES</t>
+          <t>Localização</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Turismo de natureza, hospedagem, gastronomia e atrações turísticas</t>
+          <t>Principais Produtos e Serviços</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Silêncio e ambiente intimista (6 quartos), custo menor: diárias de fim de semana lá vão de R$ 250 a R$ 3.850</t>
+          <t>Em que somos melhores que o concorrente?</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Menor reconhecimento turístico e menos infraestrutura de lazer</t>
+          <t>Em que somos piores que a concorrência</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Santa Teresa</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>A confirmar</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Santa Teresa, ES</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Turismo, gastronomia, natureza e hospedagem</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Mais tranquila e de custo menor, enquanto Santa Teresa lota em eventos (Santa Jazz com cerca de 95% de ocupação)</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Menor consolidação como destino e menos eventos, vinícolas e restaurantes</t>
+    <row r="3" ht="120" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Pedra Azul (Pousada Peterle)</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>pousadapeterle.com.br (confirmar)</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Domingos Martins, ES (BR-262, km 88)</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Chalés rústicos com lareira e hidromassagem, café colonial e loja própria de massas e biscoitos</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Preço menor e ambiente mais reservado e silencioso, com só 6 quartos. A Peterle parte de cerca de R$ 482 para casal. Atrativo próprio: cachoeira de 70 m, gratuita</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Menos reconhecimento e estrutura menor. A Peterle tem nota 9,5, loja própria e a marca de destino consolidada de Pedra Azul</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Buenos Aires</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>A confirmar</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Guarapari, ES</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Turismo de natureza, gastronomia e hospedagem</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Autenticidade, cachoeira gratuita de 70 m e custo menor, longe da agitação e da obra do mall</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Menor divulgação, mais longe do mar e com menos investimento em estrutura</t>
+    <row r="4" ht="120" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Santa Teresa (Pousada La Sofia)</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>pousadalasofia.com.br</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Santa Teresa, ES (cerca de 700 m do centro)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Pousada de estrutura nova com cerca de 9 quartos (as fontes divergem), ar-condicionado, Wi-Fi, estacionamento e restaurante aberto ao público</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Ambiente mais silencioso, longe do movimento de eventos da cidade. Cachoeira de 70 m gratuita e custo menor: a La Sofia parte de cerca de R$ 543</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Menos reconhecimento de destino e menos eventos e restaurantes por perto. A La Sofia tem estrutura nova e restaurante próprio, com nota 8,7 (35 avaliações)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="120" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Buenos Aires (Pousada Pedra d'Água)</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>A confirmar (aparece em Hotels.com e Travelocity)</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Guarapari, ES (Buenos Aires)</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Pousada com cerca de 10 quartos, piscina, churrasqueira, área de piquenique e café da manhã aos fins de semana</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Autenticidade, cachoeira de 70 m gratuita e atendimento familiar, longe da agitação e das obras do mall de Buenos Aires</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Diária parecida (cerca de R$ 250), mas Buenos Aires tem mais investimento e divulgação, e a Pedra d'Água fica mais perto de Vitória e do mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Fim da tabela</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>